--- a/validation/validation-set-manifest.xlsx
+++ b/validation/validation-set-manifest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="118">
   <si>
     <t>Run order</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Verdict</t>
-  </si>
-  <si>
     <t>Paper title</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>complete</t>
   </si>
   <si>
-    <t>Partially reproduced</t>
-  </si>
-  <si>
     <t>Testing the "Grandma Hypothesis": Characterizing Skin Microbiome Diversity as a Project-Based Learning Approach to Genomics</t>
   </si>
   <si>
@@ -103,7 +97,7 @@
     <t>phyloseq .RDS (course-processed)</t>
   </si>
   <si>
-    <t>NCBI SRA (raw reads)</t>
+    <t>NCBI SRA</t>
   </si>
   <si>
     <t>PRJNA553551</t>
@@ -130,9 +124,6 @@
     <t>Basic MetaPhlAn path, end to end</t>
   </si>
   <si>
-    <t>Reproduced</t>
-  </si>
-  <si>
     <t>Colorectal Cancer and the Human Gut Microbiome: Reproducibility with Whole-Genome Shotgun Sequencing</t>
   </si>
   <si>
@@ -145,7 +136,7 @@
     <t>MetaPhlAn taxonomic profile + HUMAnN functional profile</t>
   </si>
   <si>
-    <t>curatedMetagenomicData (Bioconductor)</t>
+    <t>curatedMetagenomicData</t>
   </si>
   <si>
     <t>study_name=VogtmannE_2016; PMID=27171425</t>
@@ -367,7 +358,7 @@
     <t>OTU/ASV table (CSV/TSV/XLS)</t>
   </si>
   <si>
-    <t>other</t>
+    <t>UCSF Dash</t>
   </si>
   <si>
     <t>10.7272/Q6RX997G</t>
@@ -719,10 +710,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1">
+    <row r="1" spans="1:19" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,514 +771,505 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2">
+        <v>2020</v>
+      </c>
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="I2">
-        <v>2020</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2">
+        <v>344</v>
+      </c>
+      <c r="P2">
+        <v>128</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+      <c r="R2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" t="s">
+      <c r="S2" t="s">
         <v>32</v>
       </c>
-      <c r="P2">
-        <v>344</v>
-      </c>
-      <c r="Q2">
-        <v>128</v>
-      </c>
-      <c r="R2">
-        <v>5</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3">
+        <v>2016</v>
+      </c>
+      <c r="I3" t="s">
         <v>38</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>39</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>40</v>
       </c>
-      <c r="I3">
-        <v>2016</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>41</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>42</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>43</v>
       </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" t="s">
-        <v>46</v>
+      <c r="O3">
+        <v>110</v>
       </c>
       <c r="P3">
         <v>110</v>
       </c>
       <c r="Q3">
-        <v>110</v>
-      </c>
-      <c r="R3">
         <v>1</v>
       </c>
+      <c r="R3" t="s">
+        <v>44</v>
+      </c>
       <c r="S3" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4">
+        <v>2020</v>
+      </c>
+      <c r="I4" t="s">
         <v>51</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>52</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>53</v>
       </c>
-      <c r="I4">
-        <v>2020</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>54</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>55</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>56</v>
       </c>
-      <c r="M4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O4" t="s">
-        <v>59</v>
-      </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
         <v>60</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="H5">
+        <v>2017</v>
+      </c>
+      <c r="I5" t="s">
         <v>61</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" t="s">
         <v>62</v>
       </c>
-      <c r="H5" t="s">
+      <c r="M5" t="s">
         <v>63</v>
       </c>
-      <c r="I5">
-        <v>2017</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
         <v>64</v>
       </c>
-      <c r="K5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" t="s">
-        <v>67</v>
-      </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
         <v>68</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="H6">
+        <v>2020</v>
+      </c>
+      <c r="I6" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>70</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" t="s">
         <v>71</v>
       </c>
-      <c r="I6">
-        <v>2020</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>72</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
         <v>73</v>
       </c>
-      <c r="L6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" t="s">
-        <v>74</v>
-      </c>
-      <c r="N6" t="s">
-        <v>75</v>
-      </c>
-      <c r="O6" t="s">
-        <v>76</v>
-      </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
         <v>77</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="H7">
+        <v>2015</v>
+      </c>
+      <c r="I7" t="s">
         <v>78</v>
       </c>
-      <c r="E7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" t="s">
         <v>79</v>
       </c>
-      <c r="H7" t="s">
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" t="s">
         <v>80</v>
       </c>
-      <c r="I7">
-        <v>2015</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7">
+        <v>120</v>
+      </c>
+      <c r="P7">
+        <v>19</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" t="s">
         <v>81</v>
       </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" t="s">
-        <v>82</v>
-      </c>
-      <c r="N7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7" t="s">
-        <v>83</v>
-      </c>
-      <c r="P7">
-        <v>120</v>
-      </c>
-      <c r="Q7">
-        <v>19</v>
-      </c>
-      <c r="R7">
-        <v>10</v>
-      </c>
-      <c r="S7" t="s">
-        <v>47</v>
-      </c>
-      <c r="T7" t="s">
-        <v>84</v>
-      </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="H8">
+        <v>2015</v>
+      </c>
+      <c r="I8" t="s">
         <v>86</v>
       </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" t="s">
         <v>87</v>
       </c>
-      <c r="H8" t="s">
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" t="s">
         <v>88</v>
       </c>
-      <c r="I8">
-        <v>2015</v>
-      </c>
-      <c r="J8" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O8" t="s">
-        <v>91</v>
+      <c r="O8">
+        <v>154</v>
       </c>
       <c r="P8">
         <v>154</v>
       </c>
       <c r="Q8">
-        <v>154</v>
-      </c>
-      <c r="R8">
         <v>1</v>
       </c>
+      <c r="R8" t="s">
+        <v>44</v>
+      </c>
       <c r="S8" t="s">
-        <v>47</v>
-      </c>
-      <c r="T8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" t="s">
         <v>93</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="H9">
+        <v>2024</v>
+      </c>
+      <c r="I9" t="s">
         <v>94</v>
       </c>
-      <c r="E9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="J9" t="s">
         <v>95</v>
       </c>
-      <c r="H9" t="s">
+      <c r="K9" t="s">
         <v>96</v>
       </c>
-      <c r="I9">
-        <v>2024</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>97</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>98</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>99</v>
       </c>
-      <c r="M9" t="s">
-        <v>100</v>
-      </c>
-      <c r="N9" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" t="s">
-        <v>102</v>
-      </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" t="s">
         <v>103</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="H10">
+        <v>2019</v>
+      </c>
+      <c r="I10" t="s">
         <v>104</v>
       </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s">
         <v>105</v>
       </c>
-      <c r="H10" t="s">
+      <c r="M10" t="s">
         <v>106</v>
       </c>
-      <c r="I10">
-        <v>2019</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="N10" t="s">
         <v>107</v>
       </c>
-      <c r="K10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" t="s">
-        <v>108</v>
-      </c>
-      <c r="N10" t="s">
-        <v>109</v>
-      </c>
-      <c r="O10" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" t="s">
         <v>111</v>
       </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="H11">
+        <v>2017</v>
+      </c>
+      <c r="I11" t="s">
         <v>112</v>
       </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="J11" t="s">
         <v>113</v>
       </c>
-      <c r="H11" t="s">
+      <c r="K11" t="s">
         <v>114</v>
       </c>
-      <c r="I11">
-        <v>2017</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>115</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>116</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>117</v>
-      </c>
-      <c r="M11" t="s">
-        <v>118</v>
-      </c>
-      <c r="N11" t="s">
-        <v>119</v>
-      </c>
-      <c r="O11" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/validation/validation-set-manifest.xlsx
+++ b/validation/validation-set-manifest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="140">
   <si>
     <t>Run order</t>
   </si>
@@ -73,6 +73,9 @@
     <t>Condition</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>A0</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
     <t>Journal of Microbiology &amp; Biology Education</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>10.1128/jmbe.v21i1.2010</t>
   </si>
   <si>
@@ -109,12 +115,24 @@
     <t>ps.RDS (619 taxa x 344 samples, with phylogeny)</t>
   </si>
   <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>skin</t>
   </si>
   <si>
     <t>wash frequency</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>S1</t>
   </si>
   <si>
@@ -130,6 +148,9 @@
     <t>PloS one</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>10.1371/journal.pone.0155362</t>
   </si>
   <si>
@@ -148,21 +169,24 @@
     <t>relative_abundance; gene_families; pathway_abundance (110 samples)</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>stool</t>
   </si>
   <si>
     <t>control/CRC</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>S4</t>
   </si>
   <si>
     <t>Second parser: BIOM, plus KEGG-orthology functional BIOM</t>
   </si>
   <si>
-    <t>pending</t>
-  </si>
-  <si>
     <t>Altered Gut Microbiome Profile in Patients With Pulmonary Arterial Hypertension</t>
   </si>
   <si>
@@ -187,6 +211,9 @@
     <t>KO_biom_table_PH.biom; taxon_biom_table_PH.biom</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>A3</t>
   </si>
   <si>
@@ -199,6 +226,9 @@
     <t>Ecosphere</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>10.1002/ecs2.1639</t>
   </si>
   <si>
@@ -211,6 +241,9 @@
     <t>all_otu_table.biom</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
@@ -250,6 +283,9 @@
     <t>Cell host &amp; microbe</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>10.1016/j.chom.2015.01.001</t>
   </si>
   <si>
@@ -259,9 +295,21 @@
     <t>relative_abundance; gene_families; pathway_abundance (120 samples)</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>control/T1D</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>S2</t>
   </si>
   <si>
@@ -283,9 +331,15 @@
     <t>relative_abundance; gene_families; pathway_abundance (154 samples)</t>
   </si>
   <si>
+    <t>154</t>
+  </si>
+  <si>
     <t>adenoma/control/CRC</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>S5</t>
   </si>
   <si>
@@ -298,6 +352,9 @@
     <t>Metabolites</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>10.3390/metabo14120713</t>
   </si>
   <si>
@@ -316,6 +373,9 @@
     <t>MetaPhlan.zip; HUMAnN.zip</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>A2</t>
   </si>
   <si>
@@ -328,6 +388,9 @@
     <t>Ecology and Evolution</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>10.1002/ece3.5789</t>
   </si>
   <si>
@@ -338,6 +401,9 @@
   </si>
   <si>
     <t>table_no_mitochondria_no_chloroplast_silva.biom</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>A4</t>
@@ -773,503 +839,503 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="s">
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>2020</v>
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2">
-        <v>344</v>
-      </c>
-      <c r="P2">
-        <v>128</v>
-      </c>
-      <c r="Q2">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="s">
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3">
-        <v>2016</v>
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
+        <v>44</v>
       </c>
       <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3">
-        <v>110</v>
-      </c>
-      <c r="P3">
-        <v>110</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
       <c r="R3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="S3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="s">
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4">
-        <v>2020</v>
+        <v>58</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5">
-        <v>3</v>
+      <c r="A5" t="s">
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" t="s">
         <v>60</v>
       </c>
-      <c r="H5">
-        <v>2017</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>61</v>
       </c>
-      <c r="J5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" t="s">
-        <v>53</v>
-      </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="N5" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6">
-        <v>4</v>
+      <c r="A6" t="s">
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6">
-        <v>2020</v>
+        <v>79</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7">
-        <v>5</v>
+      <c r="A7" t="s">
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7">
-        <v>2015</v>
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N7" t="s">
-        <v>80</v>
-      </c>
-      <c r="O7">
-        <v>120</v>
-      </c>
-      <c r="P7">
-        <v>19</v>
-      </c>
-      <c r="Q7">
-        <v>10</v>
+        <v>92</v>
+      </c>
+      <c r="O7" t="s">
+        <v>93</v>
+      </c>
+      <c r="P7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>95</v>
       </c>
       <c r="R7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="S7" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8">
-        <v>6</v>
+      <c r="A8" t="s">
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8">
-        <v>2015</v>
+        <v>101</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L8" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N8" t="s">
-        <v>88</v>
-      </c>
-      <c r="O8">
-        <v>154</v>
-      </c>
-      <c r="P8">
-        <v>154</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="O8" t="s">
+        <v>105</v>
+      </c>
+      <c r="P8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>38</v>
       </c>
       <c r="R8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="S8" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9">
-        <v>7</v>
+      <c r="A9" t="s">
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9">
-        <v>2024</v>
+        <v>111</v>
+      </c>
+      <c r="H9" t="s">
+        <v>112</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="K9" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="L9" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="N9" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10">
-        <v>8</v>
+      <c r="A10" t="s">
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
-      </c>
-      <c r="H10">
-        <v>2019</v>
+        <v>123</v>
+      </c>
+      <c r="H10" t="s">
+        <v>124</v>
       </c>
       <c r="I10" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L10" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="N10" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11">
-        <v>9</v>
+      <c r="A11" t="s">
+        <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11">
-        <v>2017</v>
+        <v>133</v>
+      </c>
+      <c r="H11" t="s">
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="K11" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="N11" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
